--- a/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181469</t>
+          <t>182396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225223</t>
+          <t>226687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132904</t>
+          <t>131496</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167995</t>
+          <t>165635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324616</t>
+          <t>324745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381890</t>
+          <t>378626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248553</t>
+          <t>247089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292307</t>
+          <t>291380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138685</t>
+          <t>141045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173776</t>
+          <t>175184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>398567</t>
+          <t>401831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>455841</t>
+          <t>455712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141535</t>
+          <t>143069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180208</t>
+          <t>182993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174059</t>
+          <t>175313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212067</t>
+          <t>213819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>331155</t>
+          <t>329030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>385034</t>
+          <t>385211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186726</t>
+          <t>183941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225399</t>
+          <t>223865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159798</t>
+          <t>158046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>197806</t>
+          <t>196552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353765</t>
+          <t>353588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407644</t>
+          <t>409769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>222115</t>
+          <t>222670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267332</t>
+          <t>268598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81209</t>
+          <t>80721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105727</t>
+          <t>106450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309554</t>
+          <t>311526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363652</t>
+          <t>366582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275057</t>
+          <t>273791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320274</t>
+          <t>319719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86573</t>
+          <t>87061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346519</t>
+          <t>343589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>400617</t>
+          <t>398645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>567162</t>
+          <t>562503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>636615</t>
+          <t>637395</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>399778</t>
+          <t>398660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>449048</t>
+          <t>456651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>984684</t>
+          <t>980415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1070372</t>
+          <t>1065684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601719</t>
+          <t>600939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>671172</t>
+          <t>675831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265237</t>
+          <t>257634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314507</t>
+          <t>315625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>882248</t>
+          <t>886936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>967936</t>
+          <t>972205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152393</t>
+          <t>151986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188841</t>
+          <t>188196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>322022</t>
+          <t>318572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>370681</t>
+          <t>369317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>484355</t>
+          <t>483920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>547731</t>
+          <t>545736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161714</t>
+          <t>162359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198162</t>
+          <t>198569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198071</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246730</t>
+          <t>250180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371576</t>
+          <t>373571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434952</t>
+          <t>435387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>57264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84212</t>
+          <t>85926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>799203</t>
+          <t>796023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>866260</t>
+          <t>862353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>864787</t>
+          <t>863143</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>940346</t>
+          <t>938164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213989</t>
+          <t>212275</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242585</t>
+          <t>240937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>382500</t>
+          <t>386407</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>449557</t>
+          <t>452737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>606614</t>
+          <t>608796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>682173</t>
+          <t>683817</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1392784</t>
+          <t>1394034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1507647</t>
+          <t>1509515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1984792</t>
+          <t>1986096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2096394</t>
+          <t>2097837</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3414032</t>
+          <t>3404040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3578311</t>
+          <t>3568526</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1762543</t>
+          <t>1760675</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1877406</t>
+          <t>1876156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1281730</t>
+          <t>1280287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1393332</t>
+          <t>1392028</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3070003</t>
+          <t>3079788</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3234282</t>
+          <t>3244274</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>198343</t>
+          <t>196732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>243067</t>
+          <t>239453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141477</t>
+          <t>142194</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178811</t>
+          <t>179107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345338</t>
+          <t>347918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>404987</t>
+          <t>404971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194144</t>
+          <t>197758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238868</t>
+          <t>240479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135643</t>
+          <t>135347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172977</t>
+          <t>172260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346678</t>
+          <t>346694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>406327</t>
+          <t>403747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>193008</t>
+          <t>195382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237826</t>
+          <t>239947</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188475</t>
+          <t>185696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227310</t>
+          <t>223689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>393049</t>
+          <t>397150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453238</t>
+          <t>453735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180971</t>
+          <t>178850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225789</t>
+          <t>223415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110701</t>
+          <t>114322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149536</t>
+          <t>152315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303570</t>
+          <t>303073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>363759</t>
+          <t>359658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>331769</t>
+          <t>334909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384467</t>
+          <t>384891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166958</t>
+          <t>165781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196714</t>
+          <t>195956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>512785</t>
+          <t>511954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>570607</t>
+          <t>573947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244948</t>
+          <t>244524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297646</t>
+          <t>294506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63415</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93171</t>
+          <t>94348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318937</t>
+          <t>315597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>376759</t>
+          <t>377590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>627763</t>
+          <t>625322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>693648</t>
+          <t>695489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>456156</t>
+          <t>454000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>509197</t>
+          <t>509879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1094476</t>
+          <t>1100000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1186204</t>
+          <t>1190245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>465361</t>
+          <t>463520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531246</t>
+          <t>533687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257460</t>
+          <t>256778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310501</t>
+          <t>312657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739463</t>
+          <t>735422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>831191</t>
+          <t>825667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>266143</t>
+          <t>266682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>310683</t>
+          <t>311180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>534032</t>
+          <t>533315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>582598</t>
+          <t>583779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>808507</t>
+          <t>815116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>881479</t>
+          <t>881465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199913</t>
+          <t>199416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>244453</t>
+          <t>243914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178924</t>
+          <t>177743</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227490</t>
+          <t>228207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390639</t>
+          <t>390653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>463611</t>
+          <t>457002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83484</t>
+          <t>84236</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114288</t>
+          <t>117094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>772321</t>
+          <t>779183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>832446</t>
+          <t>834430</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>868056</t>
+          <t>865567</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>943634</t>
+          <t>940630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>149788</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183398</t>
+          <t>182646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>276905</t>
+          <t>274921</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337030</t>
+          <t>330168</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>432599</t>
+          <t>435603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>508177</t>
+          <t>510666</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1783544</t>
+          <t>1787502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1901746</t>
+          <t>1904759</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2343648</t>
+          <t>2340512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2456436</t>
+          <t>2456362</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4157191</t>
+          <t>4163000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4325228</t>
+          <t>4313943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1520164</t>
+          <t>1517151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1638366</t>
+          <t>1634408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1093689</t>
+          <t>1093763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1206477</t>
+          <t>1209613</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2646807</t>
+          <t>2658092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2814844</t>
+          <t>2809035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172507</t>
+          <t>168658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>213778</t>
+          <t>213035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156123</t>
+          <t>156429</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194241</t>
+          <t>194818</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>337189</t>
+          <t>340243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>397325</t>
+          <t>397856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215314</t>
+          <t>216057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256585</t>
+          <t>260434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152814</t>
+          <t>152237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>190932</t>
+          <t>190626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378822</t>
+          <t>378291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438958</t>
+          <t>435904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159547</t>
+          <t>157263</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197263</t>
+          <t>197306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164837</t>
+          <t>165573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203468</t>
+          <t>204473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>336404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>389041</t>
+          <t>390186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>179921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217680</t>
+          <t>219964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168805</t>
+          <t>167800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>206700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>360459</t>
+          <t>359314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415260</t>
+          <t>413096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>264971</t>
+          <t>264580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>309409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97436</t>
+          <t>98064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121321</t>
+          <t>122223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372573</t>
+          <t>370694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>424687</t>
+          <t>425675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209928</t>
+          <t>212505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256943</t>
+          <t>257334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263349</t>
+          <t>262361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315463</t>
+          <t>317342</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>575913</t>
+          <t>574088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>644257</t>
+          <t>645111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>413921</t>
+          <t>414547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>470767</t>
+          <t>471667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1001904</t>
+          <t>1003980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1088969</t>
+          <t>1094351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505381</t>
+          <t>504527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>573725</t>
+          <t>575550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355109</t>
+          <t>354209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>411955</t>
+          <t>411329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886545</t>
+          <t>881163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>973610</t>
+          <t>971534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>304601</t>
+          <t>300960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>356920</t>
+          <t>352077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>491061</t>
+          <t>491479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>541574</t>
+          <t>541963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>806783</t>
+          <t>808005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>878148</t>
+          <t>879650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263786</t>
+          <t>268629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>316105</t>
+          <t>319746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196670</t>
+          <t>196281</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>247183</t>
+          <t>246765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>480802</t>
+          <t>479300</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>552167</t>
+          <t>550945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78172</t>
+          <t>76807</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107939</t>
+          <t>106710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>698596</t>
+          <t>700978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>759480</t>
+          <t>763766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>786739</t>
+          <t>789649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>861122</t>
+          <t>861606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179206</t>
+          <t>180435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208973</t>
+          <t>210338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>322545</t>
+          <t>318259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>383429</t>
+          <t>381047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>508048</t>
+          <t>507564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>582431</t>
+          <t>579521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1626259</t>
+          <t>1633597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1748671</t>
+          <t>1748961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2099360</t>
+          <t>2102521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2219657</t>
+          <t>2221717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3765985</t>
+          <t>3767104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3924873</t>
+          <t>3930077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1637051</t>
+          <t>1636761</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1759463</t>
+          <t>1752125</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1311939</t>
+          <t>1309879</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1432236</t>
+          <t>1429075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2992445</t>
+          <t>2987241</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3151333</t>
+          <t>3150214</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139637</t>
+          <t>140431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181676</t>
+          <t>180816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135005</t>
+          <t>135309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284231</t>
+          <t>284018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337721</t>
+          <t>343020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323536</t>
+          <t>324396</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365575</t>
+          <t>364781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278214</t>
+          <t>277208</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312462</t>
+          <t>312158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>614958</t>
+          <t>609659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>668448</t>
+          <t>668661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,19%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125991</t>
+          <t>127576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>167738</t>
+          <t>167613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100915</t>
+          <t>99695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131855</t>
+          <t>129634</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>238303</t>
+          <t>237604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>286479</t>
+          <t>285335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284475</t>
+          <t>284600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326222</t>
+          <t>324637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250725</t>
+          <t>252946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>281665</t>
+          <t>282885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>548314</t>
+          <t>549458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>596490</t>
+          <t>597189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49268</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221146</t>
+          <t>221450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64191</t>
+          <t>64089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84769</t>
+          <t>84586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>98770</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304912</t>
+          <t>302907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>447118</t>
+          <t>446814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618996</t>
+          <t>612807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82142</t>
+          <t>82325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102720</t>
+          <t>102822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>530263</t>
+          <t>532268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749525</t>
+          <t>736405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>351732</t>
+          <t>350482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>415413</t>
+          <t>417016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352189</t>
+          <t>352381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>720499</t>
+          <t>694981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>729884</t>
+          <t>734480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1190427</t>
+          <t>1251852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>619406</t>
+          <t>617803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>683087</t>
+          <t>684337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257595</t>
+          <t>283113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625905</t>
+          <t>625713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>822485</t>
+          <t>761060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1283028</t>
+          <t>1278432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160265</t>
+          <t>158013</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204746</t>
+          <t>205252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>258050</t>
+          <t>274571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>410131</t>
+          <t>414189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450348</t>
+          <t>447951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>592780</t>
+          <t>592251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270300</t>
+          <t>269794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314781</t>
+          <t>317033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431204</t>
+          <t>427146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>583285</t>
+          <t>566764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>723601</t>
+          <t>724130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866033</t>
+          <t>868430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39163</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85456</t>
+          <t>88121</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>314682</t>
+          <t>312937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>365301</t>
+          <t>363816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>368131</t>
+          <t>367038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>434962</t>
+          <t>437228</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155051</t>
+          <t>152386</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201344</t>
+          <t>199290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>396070</t>
+          <t>397555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>446689</t>
+          <t>448434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>566916</t>
+          <t>564650</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>633747</t>
+          <t>634840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>847260</t>
+          <t>860155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1171380</t>
+          <t>1171427</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1377497</t>
+          <t>1386144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1937183</t>
+          <t>1907649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2337048</t>
+          <t>2346399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2958346</t>
+          <t>3009835</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2204680</t>
+          <t>2204633</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2528800</t>
+          <t>2515905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1640575</t>
+          <t>1670109</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2200261</t>
+          <t>2191614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3995472</t>
+          <t>3943983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4616770</t>
+          <t>4607419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182396</t>
+          <t>179766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>226687</t>
+          <t>225142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131496</t>
+          <t>131124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165635</t>
+          <t>166732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324745</t>
+          <t>319893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>378626</t>
+          <t>381675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247089</t>
+          <t>248634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291380</t>
+          <t>294010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141045</t>
+          <t>139948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175184</t>
+          <t>175556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>401831</t>
+          <t>398782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>455712</t>
+          <t>460564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>143069</t>
+          <t>142632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>182993</t>
+          <t>180880</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175313</t>
+          <t>173046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213819</t>
+          <t>213407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329030</t>
+          <t>331483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>385211</t>
+          <t>386007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183941</t>
+          <t>186054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223865</t>
+          <t>224302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158046</t>
+          <t>158458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196552</t>
+          <t>198819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353588</t>
+          <t>352792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409769</t>
+          <t>407316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>222670</t>
+          <t>221295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268598</t>
+          <t>269306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80721</t>
+          <t>80384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106450</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>311526</t>
+          <t>314422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366582</t>
+          <t>365845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273791</t>
+          <t>273083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319719</t>
+          <t>321094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61332</t>
+          <t>60647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87061</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343589</t>
+          <t>344326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398645</t>
+          <t>395749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>562503</t>
+          <t>563646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>637395</t>
+          <t>632856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>398660</t>
+          <t>399718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456651</t>
+          <t>452660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>980415</t>
+          <t>976697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1065684</t>
+          <t>1067621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>600939</t>
+          <t>605478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>675831</t>
+          <t>674688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257634</t>
+          <t>261625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315625</t>
+          <t>314567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886936</t>
+          <t>884999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>972205</t>
+          <t>975923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151986</t>
+          <t>151470</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188196</t>
+          <t>189582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>318572</t>
+          <t>321798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>369317</t>
+          <t>368236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>483920</t>
+          <t>487452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>545736</t>
+          <t>547185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162359</t>
+          <t>160973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198569</t>
+          <t>199085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199435</t>
+          <t>200516</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250180</t>
+          <t>246954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>373571</t>
+          <t>372122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>435387</t>
+          <t>431855</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>56040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85926</t>
+          <t>85726</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>796023</t>
+          <t>796058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>862353</t>
+          <t>861120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>863143</t>
+          <t>857206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>938164</t>
+          <t>939075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212275</t>
+          <t>212475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240937</t>
+          <t>242161</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>386407</t>
+          <t>387640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>452737</t>
+          <t>452702</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>608796</t>
+          <t>607885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>683817</t>
+          <t>689754</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1394034</t>
+          <t>1394719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1509515</t>
+          <t>1510056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1986096</t>
+          <t>1975005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2097837</t>
+          <t>2094400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3404040</t>
+          <t>3414452</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3568526</t>
+          <t>3573479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1760675</t>
+          <t>1760134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1876156</t>
+          <t>1875471</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1280287</t>
+          <t>1283724</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1392028</t>
+          <t>1403119</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3079788</t>
+          <t>3074835</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3244274</t>
+          <t>3233862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>196732</t>
+          <t>197373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239453</t>
+          <t>240025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142194</t>
+          <t>139793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179107</t>
+          <t>178830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>347918</t>
+          <t>348278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>404971</t>
+          <t>406859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197758</t>
+          <t>197186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>240479</t>
+          <t>239838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135347</t>
+          <t>135624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172260</t>
+          <t>174661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346694</t>
+          <t>344806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>403747</t>
+          <t>403387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195382</t>
+          <t>193926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239947</t>
+          <t>238473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185696</t>
+          <t>187432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>223689</t>
+          <t>224541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>397150</t>
+          <t>395154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453735</t>
+          <t>454191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178850</t>
+          <t>180324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223415</t>
+          <t>224871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114322</t>
+          <t>113470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152315</t>
+          <t>150579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303073</t>
+          <t>302617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359658</t>
+          <t>361654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>334909</t>
+          <t>332655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384891</t>
+          <t>384914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165781</t>
+          <t>167428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195956</t>
+          <t>197191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>511954</t>
+          <t>512131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573947</t>
+          <t>571097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244524</t>
+          <t>244501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294506</t>
+          <t>296760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>62938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94348</t>
+          <t>92701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315597</t>
+          <t>318447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377590</t>
+          <t>377413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>625322</t>
+          <t>627270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>695489</t>
+          <t>699443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>454000</t>
+          <t>454843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>509879</t>
+          <t>512026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1100000</t>
+          <t>1098517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1190245</t>
+          <t>1186728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>463520</t>
+          <t>459566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533687</t>
+          <t>531739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256778</t>
+          <t>254631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>312657</t>
+          <t>311814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>735422</t>
+          <t>738939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>825667</t>
+          <t>827150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>266682</t>
+          <t>266178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>311180</t>
+          <t>309776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>533315</t>
+          <t>531476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>583779</t>
+          <t>582062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>815116</t>
+          <t>812033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>881465</t>
+          <t>881805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199416</t>
+          <t>200820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243914</t>
+          <t>244418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177743</t>
+          <t>179460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>228207</t>
+          <t>230046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390653</t>
+          <t>390313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>457002</t>
+          <t>460085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84236</t>
+          <t>81015</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>117094</t>
+          <t>115723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>779183</t>
+          <t>774324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>834430</t>
+          <t>832605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>865567</t>
+          <t>867999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>940630</t>
+          <t>938701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149788</t>
+          <t>151159</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182646</t>
+          <t>185867</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274921</t>
+          <t>276746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330168</t>
+          <t>335027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435603</t>
+          <t>437532</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510666</t>
+          <t>508234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1787502</t>
+          <t>1785733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1904759</t>
+          <t>1901606</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2340512</t>
+          <t>2338421</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2456362</t>
+          <t>2456840</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4163000</t>
+          <t>4151654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4313943</t>
+          <t>4322872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1517151</t>
+          <t>1520304</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1634408</t>
+          <t>1636177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1093763</t>
+          <t>1093285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1209613</t>
+          <t>1211704</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2658092</t>
+          <t>2649163</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2809035</t>
+          <t>2820381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168658</t>
+          <t>169406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>213035</t>
+          <t>212571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156429</t>
+          <t>155175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194818</t>
+          <t>194912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>340243</t>
+          <t>337366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>397856</t>
+          <t>395235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216057</t>
+          <t>216521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260434</t>
+          <t>259686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152237</t>
+          <t>152143</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>190626</t>
+          <t>191880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378291</t>
+          <t>380912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435904</t>
+          <t>438781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157263</t>
+          <t>161595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197306</t>
+          <t>200235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165573</t>
+          <t>166221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204473</t>
+          <t>203280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>336404</t>
+          <t>334932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390186</t>
+          <t>391419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179921</t>
+          <t>176992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219964</t>
+          <t>215632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167800</t>
+          <t>168993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206700</t>
+          <t>206052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359314</t>
+          <t>358081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413096</t>
+          <t>414568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>264580</t>
+          <t>265704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>309409</t>
+          <t>310011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98064</t>
+          <t>97502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122223</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>370694</t>
+          <t>374104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>425675</t>
+          <t>424893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212505</t>
+          <t>211903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257334</t>
+          <t>256210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43900</t>
+          <t>44283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>262361</t>
+          <t>263143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317342</t>
+          <t>313932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>574088</t>
+          <t>575353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>645111</t>
+          <t>643581</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>414547</t>
+          <t>413533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>471667</t>
+          <t>470321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1003980</t>
+          <t>1005173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1094351</t>
+          <t>1095255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504527</t>
+          <t>506057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575550</t>
+          <t>574285</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>354209</t>
+          <t>355555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>411329</t>
+          <t>412343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>881163</t>
+          <t>880259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>971534</t>
+          <t>970341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300960</t>
+          <t>302296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>352077</t>
+          <t>350213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>491479</t>
+          <t>492999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>541963</t>
+          <t>542442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>808005</t>
+          <t>807513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>879650</t>
+          <t>884518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>268629</t>
+          <t>270493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319746</t>
+          <t>318410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196281</t>
+          <t>195802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246765</t>
+          <t>245245</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>479300</t>
+          <t>474432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>550945</t>
+          <t>551437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76807</t>
+          <t>76764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106710</t>
+          <t>107428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>700978</t>
+          <t>700203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>763766</t>
+          <t>762702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>789649</t>
+          <t>787120</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>861606</t>
+          <t>861599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180435</t>
+          <t>179717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210338</t>
+          <t>210381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318259</t>
+          <t>319323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>381047</t>
+          <t>381822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507564</t>
+          <t>507571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>579521</t>
+          <t>582050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1633597</t>
+          <t>1628083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1748961</t>
+          <t>1741277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2102521</t>
+          <t>2101577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2221717</t>
+          <t>2221400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3767104</t>
+          <t>3765311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3930077</t>
+          <t>3938906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1636761</t>
+          <t>1644445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1752125</t>
+          <t>1757639</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1309879</t>
+          <t>1310196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1429075</t>
+          <t>1430019</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2987241</t>
+          <t>2978412</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3150214</t>
+          <t>3152007</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>160057</t>
+          <t>173661</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140431</t>
+          <t>151771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180816</t>
+          <t>196176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>151526</t>
+          <t>165777</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135309</t>
+          <t>148859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170259</t>
+          <t>186106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>311583</t>
+          <t>339438</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284018</t>
+          <t>312121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343020</t>
+          <t>368297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>345155</t>
+          <t>376957</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324396</t>
+          <t>354442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364781</t>
+          <t>398847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>295941</t>
+          <t>322634</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277208</t>
+          <t>302305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312158</t>
+          <t>339552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>641096</t>
+          <t>699591</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609659</t>
+          <t>670732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>668661</t>
+          <t>726908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>146340</t>
+          <t>152153</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>127576</t>
+          <t>132308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>167613</t>
+          <t>172855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>115138</t>
+          <t>125194</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99695</t>
+          <t>109392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129634</t>
+          <t>140450</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>261477</t>
+          <t>277347</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>237604</t>
+          <t>252941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285335</t>
+          <t>302953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>305873</t>
+          <t>331059</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284600</t>
+          <t>310357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324637</t>
+          <t>350904</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>267442</t>
+          <t>297949</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252946</t>
+          <t>282693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>282885</t>
+          <t>313751</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>573316</t>
+          <t>629008</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>549458</t>
+          <t>603402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>597189</t>
+          <t>653414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>135352</t>
+          <t>144604</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55457</t>
+          <t>125242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221450</t>
+          <t>162016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64089</t>
+          <t>71195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84586</t>
+          <t>93836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>209373</t>
+          <t>227051</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98770</t>
+          <t>204262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302907</t>
+          <t>250713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>532912</t>
+          <t>327008</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446814</t>
+          <t>309596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612807</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92889</t>
+          <t>105050</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82325</t>
+          <t>93661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102822</t>
+          <t>116302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>625802</t>
+          <t>432058</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>532268</t>
+          <t>408396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>736405</t>
+          <t>454847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>383057</t>
+          <t>404811</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>350482</t>
+          <t>373189</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>417016</t>
+          <t>437359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>491896</t>
+          <t>313809</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352381</t>
+          <t>291231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>694981</t>
+          <t>341080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>874953</t>
+          <t>718620</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>734480</t>
+          <t>676657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1251852</t>
+          <t>759583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>651762</t>
+          <t>727032</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617803</t>
+          <t>694484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>684337</t>
+          <t>758654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>486198</t>
+          <t>547402</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283113</t>
+          <t>520131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625713</t>
+          <t>569980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1137959</t>
+          <t>1274434</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>761060</t>
+          <t>1233471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1278432</t>
+          <t>1316397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>181404</t>
+          <t>196160</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158013</t>
+          <t>172937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205252</t>
+          <t>220287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>361159</t>
+          <t>389180</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274571</t>
+          <t>362425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>414189</t>
+          <t>412697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>542563</t>
+          <t>585340</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>447951</t>
+          <t>550660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>592251</t>
+          <t>615898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>293642</t>
+          <t>371804</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269794</t>
+          <t>347677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>317033</t>
+          <t>395027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>480176</t>
+          <t>441670</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427146</t>
+          <t>418153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>566764</t>
+          <t>468425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>773818</t>
+          <t>813474</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>724130</t>
+          <t>782916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>868430</t>
+          <t>848154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41217</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88121</t>
+          <t>75343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>340767</t>
+          <t>371728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>312937</t>
+          <t>343784</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>363816</t>
+          <t>399495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>401266</t>
+          <t>423882</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367038</t>
+          <t>389922</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>437228</t>
+          <t>461041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>180008</t>
+          <t>185074</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152386</t>
+          <t>161885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199290</t>
+          <t>201463</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>420604</t>
+          <t>472553</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>397555</t>
+          <t>444786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>448434</t>
+          <t>500497</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>600612</t>
+          <t>657627</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>564650</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>634840</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1066708</t>
+          <t>1123542</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>860155</t>
+          <t>1059302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1171427</t>
+          <t>1181847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1534507</t>
+          <t>1448136</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1386144</t>
+          <t>1398242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1907649</t>
+          <t>1504171</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2601215</t>
+          <t>2571677</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2346399</t>
+          <t>2494416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3009835</t>
+          <t>2652029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2309352</t>
+          <t>2318934</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2204633</t>
+          <t>2260629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2515905</t>
+          <t>2383174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2043251</t>
+          <t>2187257</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1670109</t>
+          <t>2131222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2191614</t>
+          <t>2237151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4352603</t>
+          <t>4506192</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3943983</t>
+          <t>4425840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4607419</t>
+          <t>4583453</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
